--- a/AAII_Financials/Yearly/OKE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OKE_YR_FIN.xlsx
@@ -1011,7 +1011,7 @@
         <v>81000</v>
       </c>
       <c r="E14" s="3">
-        <v>73000</v>
+        <v>-154000</v>
       </c>
       <c r="F14" s="3">
         <v>-621000</v>
@@ -1131,7 +1131,7 @@
         <v>27807000</v>
       </c>
       <c r="E17" s="3">
-        <v>16636000</v>
+        <v>16863000</v>
       </c>
       <c r="F17" s="3">
         <v>14226000</v>
@@ -1182,7 +1182,7 @@
         <v>5822000</v>
       </c>
       <c r="E18" s="3">
-        <v>5062000</v>
+        <v>4835000</v>
       </c>
       <c r="F18" s="3">
         <v>3451000</v>
@@ -1305,7 +1305,7 @@
         <v>7868000</v>
       </c>
       <c r="E21" s="3">
-        <v>6688000</v>
+        <v>6461000</v>
       </c>
       <c r="F21" s="3">
         <v>4511000</v>
